--- a/output/test_cases/MART_SmartSearch_QnA_Log_v1.1_20260817.xlsx
+++ b/output/test_cases/MART_SmartSearch_QnA_Log_v1.1_20260817.xlsx
@@ -377,7 +377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -575,8 +575,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Storyboard bản cập nhật v0.1-20260819 (SS-SCR-009, thành phần #7 'Hành động') đã sửa lại, xác nhận thanh hành động 'Xoá tất cả'/'Áp dụng (n)' cố định ở đáy sheet LÀ MỘT THÀNH PHẦN THẬT SỰ TỒN TẠI (không còn ghi là gap thiết kế) — khớp với ảnh Figma thật. Câu hỏi 'nguồn nào đúng' được giải quyết: Figma đúng, PPTX storyboard bản cũ (20260816) đã lỗi thời. Lưu ý: storyboard vẫn ghi 'Áp dụng (n)' có số đếm, trong khi ảnh Figma cho thấy nút chỉ ghi 'Áp dụng' không có số — điểm này vẫn còn mâu thuẫn, xem thêm QnA-39.</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="38.25" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -719,7 +727,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -737,8 +745,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Storyboard bản cập nhật v0.1-20260819 (SS-SCR-017) đã gỡ bỏ hoàn toàn đề xuất mâu thuẫn '2 giây im lặng / tối đa 15 giây' khỏi mục 'Mục cần chốt' — chỉ còn lại duy nhất giá trị 'Tự động dừng sau 6 giây' trong mô tả màn hình, không còn giá trị nào khác cạnh tranh. Xác nhận ngưỡng chính thức = 6 giây cố định.</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="38.25" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -773,7 +789,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -787,8 +803,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Storyboard bản cập nhật v0.1-20260819 (SS-SCR-010, ghi chú) nêu: 'Bộ lọc không được giữ lại mỗi khi khách đổi từ khoá tìm kiếm mới hay tự động xoá' — hiểu là bộ lọc sẽ TỰ ĐỘNG XOÁ khi khách tìm từ khoá mới (không giữ nguyên). Lưu ý: câu gốc trong storyboard hơi khó hiểu về mặt ngữ pháp (đọc như đang liệt kê 2 khả năng nối bằng 'hay' thay vì khẳng định 1 chiều) — QC tạm diễn giải theo hướng hợp lý nhất (auto-xoá) nhưng đề nghị BA xác nhận lại bằng văn bản rõ ràng hơn trước khi coi là chốt hoàn toàn.</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="63.75" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1359,7 +1383,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1377,8 +1401,16 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Xem QnA-02 — storyboard bản cập nhật v0.1-20260819 đã xác nhận thanh hành động này tồn tại thật, khớp với ảnh Figma. Vấn đề 'PPTX cũ hơn Figma' được xác nhận đúng: PPTX đã được BA cập nhật lại theo Figma mới nhất.</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="114.75" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1974,36 +2006,2147 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>QnA-30</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Loading Screen — Ngưỡng hiệu năng đa kênh (Text/Image/Voice)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-004 (Loading) hiện chỉ mô tả ngưỡng chung '&gt;300ms mới hiện Loading' và '&gt;5s → lỗi mạng', khớp với NFR-001 (Text, 300ms P95). NFR-004 (Tìm kiếm hình ảnh, 3.000ms P95) và NFR-005 (Tìm kiếm giọng nói, 4.000ms P95 — lưu ý: mâu thuẫn với FR-VS-08 ghi nhận 6 giây P95, xem thêm) có áp dụng cho component Loading dùng chung này khi tìm bằng ảnh/giọng nói không? Nếu ngưỡng lỗi mạng cố định &gt;5s dùng chung cho cả 3 kênh, một truy vấn Voice hoàn toàn bình thường (P95 hợp lệ theo NFR-005/FR-VS-08 là 4-6 giây) có nguy cơ bị hiển thị nhầm thành 'lỗi mạng' hay không?</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-004 (Storyboard) vs BRD §7 NFR-001/NFR-004/NFR-005 và §5.4 FR-VS-08</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu ngưỡng Loading UI với BRD §7 NFR đa kênh)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Chưa chốt Pass/Fail cho SS-SCR-004-SC1-TC1/TC2 khi thực thi qua kênh Image/Voice (TC hiện tại mới có dữ liệu mẫu cho kênh Text); liên quan QnA-11.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-004-SC1-TC1, SS-SCR-004-SC1-TC2</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+    </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>QnA-31</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Sponsored — Nguồn dữ liệu / tiêu chí gắn nhãn tài trợ</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>BRD chỉ mô tả FR-PR-05 gộp chung trong dải 'FR-PR-01 → FR-PR-05' (mục Ranking &amp; Sorting) với ghi chú duy nhất 'Sponsored: hàng tài trợ ghim vị trí cố định, bắt buộc gắn nhãn Được tài trợ'. Không có mô tả riêng cho FR-PR-05 về NGUỒN xác định 1 SKU là Sponsored: đến từ nền tảng đấu giá Retail Media nào, luồng nào đánh dấu SKU tài trợ, tiêu chí đủ điều kiện tham gia. Đề nghị BA cung cấp mô tả FR-PR-05 riêng biệt hoặc trỏ tới tài liệu tích hợp Retail Media liên quan.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>BRD §5.2 (dải FR-PR-01→FR-PR-05) — liên quan SS-SCR-005-SC2, SC5</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát nguồn gốc yêu cầu FR-PR-05)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>BA / Retail Media</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Không ảnh hưởng test case vị trí/nhãn hiển thị hiện có (đã test theo hành vi UI quan sát được), nhưng chặn việc viết test case tích hợp xác thực logic 'SKU nào được chọn làm Sponsored' ở tầng backend.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC2-TC1, SS-SCR-005-SC2-TC2, SS-SCR-005-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>QnA-32</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Loading/Fallback — FR-GD-01 và FR-GD-03 bị gộp chung</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>BRD gộp chung FR-GD-01 và FR-GD-03 trong cùng 1 mục 'Performance &amp; Fallback' với 2 nội dung khác nhau: (1) SLA hiệu năng tìm kiếm chung &lt;300ms P95, và (2) cơ chế Graceful Degradation — tự động hạ cấp về keyword search cơ bản khi AI Search lỗi/timeout, tuyệt đối không hiển thị lỗi kỹ thuật. Không rõ mã nào ứng với nội dung nào. Đề nghị BA tách thành 2 mục riêng biệt để trace chính xác. Ghi chú thêm: bộ test case SS-SCR-004 hiện tại mới kiểm tra ngưỡng hiển thị UI Loading (theo storyboard), CHƯA có test case nào kiểm tra hành vi Graceful Degradation thực tế khi AI Search sập — cần bổ sung sau khi REQ được tách rõ.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>BRD §5.2 (dòng 'FR-GD-01, FR-GD-03') — toàn bộ SS-SCR-004</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu REQ ID gộp trong BRD)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Cột REQ ID của toàn bộ test case SS-SCR-004 hiện dùng chung 1 chuỗi 'FR-GD-01, FR-GD-03' không tách bạch; thiếu hẳn 1 nhóm test case cho hành vi Graceful Degradation (chưa có TC nào trong bản này).</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-004-SC1-TC1, SC1-TC2, SC2-TC1, SC3-TC1</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>QnA-33</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Search Results — Trạng thái nền sau khi xoá từ khoá bằng (✕)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC2 quy định: tap (✕) trên Search Bar → ô nhập xoá trắng, chuyển sang Autocomplete Screen. Nhưng chưa quy định trạng thái của trang kết quả PHÍA SAU lớp Autocomplete lúc đó: filter chip đang áp dụng (VD 'Không đường') và danh sách sản phẩm đang hiển thị trước đó có được GIỮ NGUYÊN (ẩn phía sau, sẵn sàng khôi phục nếu khách đóng Autocomplete mà không tìm từ mới) hay bị XOÁ/RESET ngay khi tap (✕)?</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3 (Storyboard không mô tả trạng thái nền)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung theo yêu cầu review)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-005-SC3-TC3 không chấm Pass/Fail cụ thể cho tới khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC3</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Chế độ xem (Grid/List) lưu Local Storage — đổi thiết bị / đổi tài khoản</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>FR-PR-07 quy định chế độ xem lưu tại Local Storage CỦA THIẾT BỊ, không phải theo tài khoản server-side. Hai trường hợp chưa được quy định: (1) Thành viên đăng nhập lần đầu trên thiết bị B (đã từng chọn List trên thiết bị A) — thiết bị B có đồng bộ chế độ List từ tài khoản hay luôn mặc định Grid theo state riêng của thiết bị? (2) Hai tài khoản khác nhau đăng nhập lần lượt trên CÙNG 1 thiết bị (Account 1 chọn List rồi logout, Account 2 login) — Account 2 có kế thừa List (vì lưu theo thiết bị) hay có cơ chế lưu riêng theo user?</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1 / SS-SCR-006-SC1 vs BRD FR-PR-07 (chỉ nói 'lưu trạng thái tại Local Storage', không nói phạm vi theo thiết bị hay theo tài khoản)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-005-SC1-TC3/TC4 và SS-SCR-006-SC1-TC3/TC4 không chấm Pass/Fail cho tới khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC3, SS-SCR-005-SC1-TC4, SS-SCR-006-SC1-TC3, SS-SCR-006-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>QnA-35</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Rating hiển thị cho sản phẩm chưa có đánh giá (0 review)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>BRD không quy định cách hiển thị rating khi SKU chưa có review nào — ẩn hẳn phần sao, hay hiện text 'Chưa có đánh giá'? Yêu cầu tối thiểu đã thống nhất khi biên soạn test case: KHÔNG hiển thị '0.0 ★ (0)' hay giá trị NaN/rỗng gây phản cảm, nhưng cách hiển thị thay thế cụ thể chưa được chốt.</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC3 (trước đây gắn nhầm tham chiếu QnA-04 — nội dung QnA-04 thực chất nói về ngưỡng debounce/fuzzy-match/confidence, không liên quan tới hiển thị rating; đã tách thành mục riêng này để tra cứu chính xác, xem thêm ghi chú tại QnA-04)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>QC (phát hiện khi rà soát chéo QnA Ref không khớp giữa QnA-04 và SS-SCR-006-SC3-TC1)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-006-SC3-TC1 không chấm Pass/Fail theo cách hiển thị cụ thể cho tới khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC3-TC1</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>QnA-36</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Correct Banner — Gợi ý song ngữ (ngôn ngữ đang nhập + ngôn ngữ hệ thống)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>FR-AC-01 chỉ mô tả 1 banner gợi ý duy nhất dạng 'Bạn muốn tìm [Từ đúng]?', không mô tả hành vi hiển thị ĐỒNG THỜI 2 gợi ý khi khách gõ từ khoá bằng ngôn ngữ khác với ngôn ngữ hệ thống (VD: UI=VI, khách gõ tiếng Anh/Nga) — cụ thể là: gợi ý theo đúng ngôn ngữ đang nhập (ưu tiên hiển thị trước) VÀ thêm 1 gợi ý tương đương bằng tiếng Việt (ngôn ngữ hệ thống đang hiển thị). Cơ chế song ngữ này cũng chưa được FR-SM-02 (đa ngôn ngữ) hay FR-SM-04 (đồng nghĩa) nhắc tới. Đề nghị BA xác nhận đây có phải hành vi mong muốn của v1 không, và nếu có, quy định rõ định dạng hiển thị 2 gợi ý cùng lúc.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4 vs BRD FR-AC-01, FR-SM-02, FR-SM-04 (không đề cập gợi ý song ngữ đồng thời)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>QC (yêu cầu bổ sung testcase từ review lần 3)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-003-SC4-TC2/TC3 không chấm Pass/Fail theo hành vi song ngữ cụ thể cho tới khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4-TC2, SS-SCR-003-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Sort — Định nghĩa &amp; quy tắc tie-break của từng tuỳ chọn ('logic hệ thống cũ' QC không có visibility)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-PR-06 chỉ ghi '7 tuỳ chọn còn lại... giữ nguyên logic sorting như hệ thống cũ' mà không mô tả cụ thể logic đó. Ảnh Figma thực tế (Text Search.png) có phụ đề ngắn cho từng tuỳ chọn ('Lượt mua cao nhất', 'Được quan tâm nhiều', '% khuyến mãi cao nhất', 'Sao trung bình cao nhất', 'Rẻ nhất lên trên', 'Đắt nhất lên trên', 'Theo thứ tự bảng chữ cái') nhưng không đủ chi tiết kỹ thuật để QC tự viết test case định lượng chính xác. Cụ thể cần BA/TD xác nhận: (1) 'Lượt mua' tính theo Order Count hay Item Quantity (và khung thời gian)? (2) 'Được quan tâm' tính theo PDP view hay impression trong kết quả tìm kiếm, khung thời gian nào? (3) 'Sao trung bình' là trung bình thô hay có làm mượt theo số lượng review (Bayesian/weighted) để tránh 1 SKU-1-review-5-sao áp đảo SKU nhiều review hơn? (4) Quy tắc tie-break khi nhiều SKU trùng giá ở Sort theo Giá là gì?</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1 vs BRD FR-PR-06 ('giữ nguyên logic hệ thống cũ' — không có chi tiết) và ảnh Figma Text Search.png (chỉ có phụ đề ngắn, không đủ chi tiết kỹ thuật)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung, không thể verify logic hệ thống cũ nếu không có tài liệu)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Các test case mới SS-SCR-008-SC1-TC3 đến TC9 (theo từng tuỳ chọn Sort) không chấm Pass/Fail định lượng chi tiết cho tới khi có định nghĩa chính thức.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3, TC4, TC5, TC6, TC7, TC8</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>QnA-38</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Smart Filter — Công thức sinh Tag (Information Gain) &amp; thứ tự hiển thị (FR-SF-03)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>FR-SF-03 (trong dải gộp FR-SF-01→FR-SF-03) chỉ mô tả 'AI bốc ra tối đa 10 Tag lọc thông minh có Information Gain cao nhất... cấu trúc phẳng, không gom nhóm'. Không có mô tả: công thức tính Information Gain, ngưỡng tối thiểu để 1 tag đủ điều kiện hiển thị, và thứ tự hiển thị các chip (theo Information Gain giảm dần? theo nhóm thuộc tính?). Áp dụng cho cả khối Smart Filter Chips trên trang kết quả (SS-SCR-005-SC9) và tab Nhãn trong Bộ lọc chi tiết (SS-SCR-009, vì theo FR-SF-04 tab Nhãn 'Dựa vào danh sách smart filter' — cùng 1 nguồn dữ liệu).</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9 / SS-SCR-009-SC3 vs BRD FR-SF-01→03</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-009-SC3-TC2 không chấm Pass/Fail chi tiết cho tới khi có công thức chính thức.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC3-TC2</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>QnA-39</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Bộ lọc — Badge số lượng: theo từng tab (Figma có) vs badge tổng trên nút Bộ lọc (Figma không có)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Đối chiếu lại ảnh Figma thực tế (Text Search.png, đã tăng sáng — xem QnA-16) phát hiện: (1) BÊN TRONG sheet Bộ lọc, mỗi tab (Danh mục/Nhãn/Giao hàng/Đánh giá/Giá) CÓ badge số riêng đúng bằng số điều kiện đang chọn trong tab đó (VD tab Nhãn chọn 3 chip → badge='3') — chi tiết này không được PPTX storyboard hay BRD nhắc tới. (2) Nút 'Áp dụng' ở đáy sheet KHÔNG có số '(n)' kèm theo như mô tả trong Storyboard ('Chạm Áp dụng (n)'). (3) Quan trọng nhất: nút 'Bộ lọc' trên trang kết quả (SS-SCR-005, bên ngoài sheet) KHÔNG hiển thị badge số nào ngay cả khi đã áp dụng 3 điều kiện lọc — mâu thuẫn trực tiếp với giả định 'badge nút Bộ lọc = tổng số điều kiện đang áp dụng' hiện đang dùng trong test case SS-SCR-009-SC1-TC1 và toàn bộ scenario SS-SCR-010 (Filter Applied State). Đề nghị BA/UX xác nhận: ảnh Figma này có phải bản mới nhất không, và badge tổng trên nút Bộ lọc thực sự có tồn tại hay không — nếu không, cả bộ SS-SCR-010 cần được viết lại theo cơ chế hiển thị khác (VD danh sách chip filter hiển thị trực tiếp thay vì badge số). [Cập nhật 19/08/2026: storyboard bản mới nhất (v0.1-20260819) VẪN giữ nguyên chữ 'Áp dụng (n)' có số đếm trong mô tả màn hình SS-SCR-009 — xác nhận mâu thuẫn với ảnh Figma (không có số) vẫn còn tồn tại ở phiên bản tài liệu mới nhất, chưa được đồng bộ.]</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Text Search.png (Figma thực tế) vs Storyboard PPTX + BRD — liên quan QnA-02/QnA-18 (cùng nguồn ảnh, phát hiện thêm chi tiết mới)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu badge trong ảnh Figma thực tế với giả định đang dùng trong bộ test case)</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng lớn: có thể làm sai toàn bộ giả định "badge tổng" đang dùng ở SS-SCR-009-SC1-TC1 và SS-SCR-010-SC1-TC1/SC2-TC1/SC3-TC1 (các test case này KHÔNG được sửa trong lần cập nhật này, chỉ ghi nhận rủi ro tại đây — cần rà soát lại một khi có xác nhận chính thức). Test case mới SS-SCR-009-SC6-TC3 không chấm Pass/Fail cho tới khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC3 (mới); cảnh báo rủi ro cho SS-SCR-009-SC1-TC1, SS-SCR-010-SC1-TC1, SS-SCR-010-SC2-TC1, SS-SCR-010-SC3-TC1 (chưa sửa)</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>QnA-40</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Data-prep — Bộ test chuẩn Smart Search (golden set)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>"Từ liên quan" (dimension "related" trong ma trận biến thể từ khoá) chưa có định nghĩa kỹ thuật thống nhất. 3 cách hiểu cho ra kỳ vọng khác nhau: (1) Co-purchase — sản phẩm hay được mua kèm cùng đơn hàng; (2) Category-sibling — cùng ngành hàng/category con; (3) Complementary — bổ trợ công năng (VD: "sữa tươi" -&gt; "ngũ cốc", "mật ong"). Cần BA chọn 1 cơ chế (hoặc kết hợp có trọng số) trước khi curate data/glossary/related_terms.csv và sinh test case cho dimension này.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Test Strategy Artifact - Phần 1.2, 1.6 (data/glossary/related_terms.csv)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>QC (Claude, theo yêu cầu đánh giá pipeline test Smart Search, 19/08/2026)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Chặn việc curate data/glossary/related_terms.csv (hiện chỉ có 1 dòng ví dụ placeholder chưa dùng được) và chặn việc sinh test case thật cho dimension "related" trong bộ golden test set.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>QnA-40</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Danh mục — Quy tắc hiển thị 'Tất cả trong [Tên danh mục]' &amp; hành vi breadcrumb 'Tất cả danh mục'</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Ảnh Figma thực tế (Text Search.png) xác nhận: khi khách drill-down vào 1 danh mục cha có danh mục con (VD 'Thực phẩm &amp; Đồ uống › Sữa &amp; Trứng'), hệ thống hiển thị 1 lựa chọn radio 'Tất cả trong "Sữa &amp; Trứng"' (được chọn sẵn/mặc định) phía trên danh sách danh mục con — chọn lựa chọn này áp dụng lọc theo TOÀN BỘ nhánh 'Sữa &amp; Trứng' (không thu hẹp về 1 danh mục con cụ thể nào). Điều này xác nhận đúng theo mô tả QC nêu ra. Tuy nhiên hành vi của link breadcrumb '‹ Tất cả danh mục' ở đầu (khác với các mục breadcrumb trung gian như 'Thực phẩm &amp; Đồ uống') chưa được thể hiện rõ qua ảnh tĩnh: tap vào đây có (a) quay thẳng về danh sách danh mục cấp cao nhất (root) VÀ đồng thời bỏ chọn hoàn toàn điều kiện Danh mục đang có (badge tab Danh mục về 0), hay (b) chỉ đơn thuần điều hướng UI về root mà KHÔNG bỏ chọn lựa chọn Danh mục đã xác nhận trước đó (giữ nguyên badge=1, khách phải tự chọn lại/tap Áp dụng để đổi)? Đề nghị BA/UX xác nhận.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4 vs ảnh Figma thực tế (Text Search.png) — breadcrumb 'Tất cả danh mục' không được demo tương tác trong ảnh tĩnh</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu ảnh Figma thực tế theo yêu cầu review)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-009-SC4-TC3 không chấm Pass/Fail cho tới khi xác nhận; SC4-TC2 ('Tất cả trong X') có thể chấm Pass/Fail vì đã có bằng chứng ảnh Figma xác nhận cơ chế hiển thị.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC2, SS-SCR-009-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>QnA-41</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Bộ lọc Giá — percentile tính trên giá gốc (list price) hay giá sau khuyến mãi (giá bán thực tế)?</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>BRD chỉ mô tả '3 option range giá gợi ý tự động... chia theo percentile của tập kết quả' mà không nói rõ percentile tính trên GIÁ GỐC (list price, trước giảm giá) hay GIÁ SAU KHUYẾN MÃI (giá khách thực trả). Đây là khác biệt quan trọng: nhiều SKU trong tập kết quả có badge giảm giá (VD -13%, -11% theo ảnh Figma); nếu percentile tính theo giá gốc, 1 SKU cao cấp đang giảm giá sâu có thể bị xếp nhầm vào nhóm 'giá cao' dù giá khách thực trả lại thuộc nhóm 'giá thấp', gây trải nghiệm lọc sai lệch với kỳ vọng của khách hàng (khách lọc theo giá đang trả, không phải giá niêm yết).</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2 vs BRD FR-SF-04 (mục Giá — không nêu rõ cơ sở tính giá)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>BA / Merchandising</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-009-SC2-TC2 không chấm Pass/Fail định lượng chính xác cho tới khi xác nhận cơ sở tính giá.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>QnA-42</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Giao hàng — BRD chỉ liệt kê 1 giá trị duy nhất, chưa rõ có bao nhiêu loại hình giao hàng</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>FR-SF-04 mô tả tab 'Giao hàng' trong Bộ lọc chi tiết chỉ với đúng 1 dòng 'Giao hàng tiêu chuẩn', không có danh sách nhiều lựa chọn như các tab khác (Đánh giá liệt kê đủ 5 mức, Danh mục/Nhãn/Giá đều có logic rõ ràng). Không có ghi chú 'Chỉ chọn 1' hay 'Chọn nhiều' cho nhóm này như các nhóm khác. Cần BA xác nhận: (1) đây có đúng là toàn bộ danh sách (chỉ 1 loại hình giao hàng tiêu chuẩn tồn tại ở v1, tab về bản chất là 1 checkbox bật/tắt), hay còn thiếu các loại hình khác chưa liệt kê (VD Giao hoả tốc, Giao trong ngày, Giao theo khung giờ hẹn trước) mà BA quên đưa vào tài liệu; (2) nếu chỉ có 1 giá trị, cấu trúc UI có thực sự cần 1 tab riêng hay nên gộp thành 1 chip/toggle đơn giản hơn?</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009 (tab Giao hàng) vs BRD FR-SF-04 (chỉ liệt kê 'Giao hàng tiêu chuẩn')</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-009-SC9-TC1 không chấm Pass/Fail chi tiết (số lượng lựa chọn, cấu trúc UI) cho tới khi xác nhận danh sách đầy đủ.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9-TC1</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>Storyboard bản cập nhật v0.1-20260819 (SS-SCR-009, thành phần #6) xác nhận rõ: 'Giao hàng &amp; các nhóm khác || Checkbox "Giao hàng tiêu chuẩn"' — xác nhận đây là ĐÚNG 1 checkbox bật/tắt duy nhất, không có loại hình giao hàng nào khác trong v1. Câu hỏi (1) đã được trả lời: đúng, đây là toàn bộ danh sách. Câu hỏi (2) về cấu trúc UI (có cần tách tab riêng không) vẫn để tuỳ đội UI quyết định, không ảnh hưởng tới hành vi test.</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>QnA-43</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Graceful Degradation — ngưỡng SLA có được nới lỏng trong chế độ fallback Keyword search không?</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>FR-GD-01/NFR-001 quy định SLA 300ms P95 cho chế độ tìm kiếm AI bình thường; FR-GD-03/NFR-009 quy định khi AI Search sập thì hệ thống tự động hạ cấp (Graceful Degradation) sang thuật toán Keyword cơ bản, không hiển thị lỗi cho khách. Tuy nhiên BRD không nói rõ: trong lúc đang chạy ở CHẾ ĐỘ FALLBACK (Keyword cơ bản), ngưỡng hiệu năng 300ms P95 có tiếp tục áp dụng nguyên vẹn hay được nới lỏng/thắt chặt khác đi (do thuật toán keyword đơn giản hơn AI, có thể nhanh hơn hẳn, nhưng cũng có thể chậm hơn nếu hạ tầng keyword search cũ chưa được tối ưu cho tải hiện tại)?</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>INT-13-SC2 (Graceful Degradation) vs BRD §7 NFR-001/NFR-009 (không nói rõ ngưỡng SLA áp dụng trong chế độ fallback)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung khi viết test case Graceful Degradation)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới INT-13-SC2-TC2 không chấm Pass/Fail định lượng cho tới khi xác nhận ngưỡng SLA áp dụng trong chế độ fallback.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>INT-13-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>QnA-44</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Zero Result vs Out-of-stock — ranh giới kích hoạt khi TẤT CẢ SKU khớp chính xác đều hết hàng</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>FR-PR-01→05 quy định quy tắc ghi đè (Override) cho Out-of-stock: 'Bị ép xuống đáy danh sách (bỏ qua điểm)' — tức SKU hết hàng VẪN hiển thị trên trang kết quả (SS-SCR-005), chỉ bị đẩy xuống cuối, KHÔNG bị loại khỏi kết quả. Điều này ngụ ý: nếu khách tìm đúng 1 từ khoá khớp chính xác 1 SKU đang hết hàng nhưng còn nhiều SKU khác (cùng khớp từ khoá) đang còn hàng, hệ thống vẫn ở lại SS-SCR-005 bình thường (SKU hết hàng chỉ nằm cuối danh sách) — Zero Result Page (SS-SCR-012) sẽ KHÔNG được kích hoạt, đồng nghĩa khối 'Có thể bạn sẽ thích' của SS-SCR-012 cũng không xuất hiện cho trường hợp này. Tuy nhiên, chưa có tài liệu nào nói rõ TRƯỜNG HỢP BIÊN: nếu TẤT CẢ SKU khớp trực tiếp với từ khoá đều đang hết hàng (không còn SKU nào khớp trực tiếp còn hàng) — hệ thống có (a) vẫn hiển thị SS-SCR-005 với (các) SKU hết hàng đó (dù không mua được ngay), hay (b) coi như tương đương '0 kết quả có thể mua' và chuyển hướng sang luồng Zero Result Page (SS-SCR-012, kích hoạt khối gợi ý Substitute/Cross-sell/Best-seller)?</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-012 vs BRD FR-PR-01→05 (Out-of-stock override chỉ mô tả cho trường hợp có SKU khác còn hàng trong cùng tập kết quả, không nói rõ trường hợp toàn bộ đều hết hàng)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát ranh giới kích hoạt Zero Result theo yêu cầu review)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>BA / PO</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-012-SC4-TC2 không chấm Pass/Fail cho tới khi xác nhận; SC4-TC1 (còn SKU khác còn hàng) có thể chấm Pass/Fail vì đã có quy tắc Out-of-stock override rõ ràng trong BRD.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4-TC1, SS-SCR-012-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>QnA-45</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Cross-sell (Basket Analysis) — công thức/thuật toán xác định sản phẩm gợi ý bán kèm</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>BRD chỉ mô tả 'Cross-sell (Basket Analysis): Khai thác lịch sử đơn hàng để tìm ra hàng mua kèm (Bia Corona có trong lịch sử đơn hàng → Gợi ý Mồi nhậu/Đậu phộng)' — không có công thức cụ thể. Cần BA/TD xác nhận: (1) thuật toán nền tảng là gì (association rule mining/market basket analysis kiểu Apriori, hay đơn giản là đếm đồng xuất hiện — co-occurrence count)? (2) có ngưỡng tối thiểu (minimum support/confidence) để 1 cặp sản phẩm đủ điều kiện gợi ý không? (3) dữ liệu tính trên TOÀN HỆ THỐNG (aggregate toàn bộ khách hàng) hay cá nhân hoá riêng theo lịch sử mua của từng khách? (4) khung thời gian dữ liệu đơn hàng dùng để tính (all-time hay rolling window, giống cơ chế 3-6 tháng của 'Thường mua' FR-PS-03 không)?</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1 vs BRD FR-ZR-02 (Cross-sell — chỉ có ví dụ minh hoạ, không có công thức)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD / Data</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-012-SC1-TC4 chỉ verify được hành vi bề mặt (gợi ý có liên quan hợp lý, không ngẫu nhiên), không thể verify chính xác thuật toán cho tới khi có công thức chính thức.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>QnA-46</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Zero Result — 'Có thể bạn sẽ thích' mặc định 10 sản phẩm, số lượng tối đa là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>BRD chỉ ghi 'Áp dụng Lazy Loading, mặc định hiển thị 10 sản phẩm' cho khối 'Có thể bạn sẽ thích' — không nói rõ giới hạn tối đa khi khách tiếp tục cuộn (tải thêm vô hạn theo lazy load, hay dừng lại ở 1 ngưỡng cụ thể, VD 30/50 sản phẩm)? Đặc biệt quan trọng với tầng fallback sâu nhất (Best-seller toàn hệ thống) vì về lý thuyết danh sách bán chạy có thể rất dài.</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1 vs BRD FR-ZR-02 (chỉ nêu mặc định 10, không nêu giới hạn tối đa)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-012-SC1-TC5 không chấm Pass/Fail định lượng (số lượng tối đa cụ thể) cho tới khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>QnA-47</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Cấu hình Từ điển Cấm (Profanity Filter) &amp; Xu hướng tìm kiếm — có cho phép config thủ công qua CMS không?</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Storyboard bản cập nhật v0.1-20260819 (Slide 26, Mục cần chốt #3) nêu 2 vấn đề mới cần làm rõ: (1) Từ điển cấm (Profanity Filter) dùng để lọc từ khoá xu hướng (FR-PS-02) có cho phép Vận hành viên (OP) cấu hình thủ công qua CMS không, hay hoàn toàn tự động theo danh sách cố định? (2) Xu hướng tìm kiếm (Trending Search) có cho phép config tay (VD ghim/ẩn 1 từ khoá cụ thể) không, hay hoàn toàn tính tự động theo thuật toán Trending Score?</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-001 (Storyboard v0.1-20260819, Slide 26 'Mục cần chốt' #3)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung sau khi storyboard cập nhật ngày 19/08/2026)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>BA / Mart</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Chưa có test case nào kiểm tra khả năng cấu hình thủ công của 2 khối này (Từ điển cấm, Xu hướng tìm kiếm) — cần bổ sung TC sau khi có quyết định (nếu CMS tồn tại, cần test riêng cho luồng Admin/CMS, ngoài phạm vi UI khách hàng hiện tại).</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>N/A — cần bổ sung TC sau khi có đặc tả</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>QnA-48</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Bộ lọc Danh mục — giữ nguyên 5 cấp phân cấp hay chỉ cho chọn ở cấp lá (leaf node)?</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Storyboard bản cập nhật v0.1-20260819 (Slide 26, Mục cần chốt #4) đặt câu hỏi mới: 'Cây danh mục trong bộ lọc có giữ nguyên việc hiển thị đầy đủ 5 cấp phân cấp như hiện tại không, hay chỉ hiển thị/cho phép thao tác chọn ở cấp độ nhỏ nhất (leaf node)?' Câu hỏi này ẢNH HƯỞNG TRỰC TIẾP tới bộ test case SS-SCR-009-SC4 (đã viết dựa trên bằng chứng ảnh Figma cho thấy có lựa chọn 'Tất cả trong [Tên danh mục]' ở CẤP TRUNG GIAN, không chỉ ở cấp lá) và QnA-40 (hành vi breadcrumb 'Tất cả danh mục'). Nếu quyết định cuối cùng là 'chỉ cho chọn ở cấp lá', lựa chọn 'Tất cả trong X' ở cấp trung gian có thể sẽ bị loại bỏ khỏi thiết kế — cần BA/UX xác nhận trước khi coi bộ test case SC4 hiện tại là đúng thiết kế cuối cùng.</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009 (Storyboard v0.1-20260819, Slide 26 'Mục cần chốt' #4) — liên quan QnA-40, SS-SCR-009-SC4-TC1/TC2/TC3</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung sau khi storyboard cập nhật ngày 19/08/2026)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>BA / Mart</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Có nguy cơ làm sai lệch toàn bộ giả định của SS-SCR-009-SC4-TC1 (xác nhận có lựa chọn 'Tất cả trong X' ở cấp trung gian dựa trên ảnh Figma) nếu quyết định cuối cùng là chỉ cho chọn cấp lá — cần rà soát lại SC4-TC1 một khi có xác nhận chính thức.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC1, SS-SCR-009-SC4-TC2, SS-SCR-009-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>QnA-49</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Gallery — Nhãn phân loại trên ảnh trong khay 'Ảnh gần đây': rule sinh nhãn là gì? Và có thực sự là ảnh từ thư viện thiết bị không?</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Ảnh Figma thực tế (Image Search.png, slide 19/SS-SCR-014) cho thấy lưới 'Ảnh gần đây' hiển thị 12 ô, MỖI Ô CÓ NHÃN PHÂN LOẠI dạng banner ở đáy (VD: 'Sữa', 'Rau cải', 'Trứng', 'Thịt', 'Táo', 'Cá', 'Pho mai', 'Sữa chua', 'Bông cải', 'Mật ong', 'Nước', 'Dâu tây') — chi tiết này KHÔNG được mô tả trong bảng thành phần của storyboard (chỉ có 5 dòng, không nhắc tới nhãn). Cần BA/UX xác nhận: (1) Nhãn phân loại này được sinh ra như thế nào — AI tự nhận diện nội dung ảnh và gắn nhãn, hay đây là metadata/tên file có sẵn từ thư viện? (2) QUAN TRỌNG HƠN: các ô trong ảnh mockup trông giống ICON MINH HOẠ CHUNG (illustration) theo từng danh mục sản phẩm, KHÔNG giống ảnh chụp thực tế từ thư viện cá nhân của người dùng — điều này MÂU THUẪN với mô tả storyboard 'Ảnh gần đây — chỉ lấy ảnh mới nhất trong thư viện, sắp xếp giảm dần theo thời gian' (ngụ ý đây phải là ảnh thật của khách, không phải icon minh hoạ chung). Cần xác nhận đây có phải chỉ là placeholder minh hoạ cho mockup (không phản ánh thiết kế thật), hay đúng là thiết kế cuối cùng sẽ hiển thị nhãn phân loại AI trên ảnh thật của khách.</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-014 (Storyboard, Slide 19, thành phần #5 'Lưới ảnh') vs ảnh Figma thực tế (Image Search.png) — không khớp với mô tả text</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu ảnh Figma thực tế Image Search.png với bảng mô tả storyboard)</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Chưa có test case nào verify nhãn phân loại trên ảnh (vì chưa rõ đây là placeholder hay thiết kế thật); nếu là thiết kế thật, cần bổ sung TC riêng kiểm tra độ chính xác gắn nhãn AI sau khi có quyết định.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>N/A — cần bổ sung TC sau khi xác nhận</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>QnA-50</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Màn hình lỗi nhận diện ảnh/giọng nói — nút 'Back' trên header dẫn tới đâu, có trùng với CTA 'Thử lại' không?</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-016 (Không nhận diện được ảnh) và SS-SCR-019 (Không nhận diện được giọng nói) đều có nút 'Back' ở header ('Tiêu đề ... + nút Back — khách luôn biết mình đang ở luồng nào') NGOÀI 2 CTA chính đã có: 'Thử lại' (quay lại Camera/Listening Screen, giữ chế độ trước đó) và 'Tìm bằng từ khoá' (chuyển sang Pre-search). Storyboard không nói rõ nút Back dẫn tới đâu: (a) trùng hành vi với 'Thử lại' (quay lại Camera/Listening Screen) — khiến 2 nút làm cùng 1 việc, hay (b) thoát hẳn khỏi luồng tìm bằng ảnh/giọng nói, quay thẳng về màn hình đã mở luồng này (thường là Pre-search hoặc trang kết quả trước đó) — khác với cả 2 CTA chính?</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-016, SS-SCR-019 (Storyboard) — nút Back chỉ được nhắc tên, không mô tả đích đến</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Test case mới SS-SCR-016-SC1-TC3 không chấm Pass/Fail cho tới khi xác nhận đích đến của nút Back.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-016-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>QnA-51</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Voice Search — Banner gợi ý khi confidence nhận diện trung bình-thấp (SS-SCR-018-SC1-TC3): tính năng này có thực sự nằm trong scope v1 không?</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Storyboard (SS-SCR-018, thành phần #7 'Nhận diện sai một phần') mô tả: 'Nếu độ tin cậy trung bình thấp, hiển thị banner 'Bạn có muốn tìm …?' tương tự SS-SCR-003 thay vì trả kết quả sai.' Tuy nhiên: (1) BRD (FR-VS-04/FR-VS-05) hoàn toàn KHÔNG nhắc tới cơ chế banner độ tin cậy này — chỉ mô tả luồng điều hướng thẳng + cho sửa tay bằng bàn phím, không có bước xác minh trung gian nào (kể cả banner). (2) Chưa có ngưỡng confidence cụ thể được chốt (đã ghi nhận ở QnA-04). Cần BA/TD xác nhận: tính năng banner gợi ý cho voice search có thực sự nằm trong scope v1 hay chỉ là ý tưởng ghi chú thêm của storyboard chưa được BRD phê duyệt chính thức?</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-018 (Storyboard, thành phần #7) vs BRD FR-VS-04/FR-VS-05 (không nhắc tới cơ chế này)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu storyboard với BRD, phát hiện khi rà soát SS-SCR-018-SC1-TC3)</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-018-SC1-TC3 không chấm Pass/Fail cho tới khi xác nhận tính năng này có thực sự trong scope v1 hay không.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>QnA-52</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Admin Ranking Scorecard — 0% test coverage, có test plan riêng không?</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>BRD §3.1 liệt kê 'Bảng điểm Xếp hạng Quản trị' là hạng mục #10 trong phạm vi, và BO-05 mô tả rõ đội Merchandising cần chỉnh trọng số xếp hạng real-time không cần deploy code. Tuy nhiên Storyboard (slide 4, 'Ngoài phạm vi') tự loại 'backoffice cấu hình từ khoá và Retail Media' khỏi phạm vi 19 màn hình — nên toàn bộ Combined Test Suite (bám theo Storyboard) không hề đụng tới Admin/backoffice. Có test plan Admin/backoffice riêng đang được lên kế hoạch hay chuẩn bị bởi đội khác không, hay đây là gap thật chưa ai phụ trách?</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>BRD §3.1 hạng mục #10, BO-05 vs Storyboard slide 4 'Ngoài phạm vi'</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát phạm vi tổng thể BRD vs Storyboard)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>PO / BA</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Không có test case nào trong bộ này (UI hay Integration) kiểm tra chức năng Admin Scorecard — nếu đây thực sự trong scope go-live, cần một test suite hoàn toàn riêng.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>N/A — không có TC nào trong bộ test này</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>QnA-53</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>FR-SP-02 và FR-ZR-01 — 2 mã REQ ID không tồn tại trong BRD nhưng đang dùng rộng rãi trong test suite</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Đối chiếu toàn văn BRD xác nhận: (1) FR-SP-02 KHÔNG xuất hiện ở bất kỳ đâu trong BRD (Storyboard tự gắn mã này cho SS-SCR-001, kéo theo toàn bộ ~17 test case của màn Pre-search dùng REQ ID không có định nghĩa); (2) FR-ZR-01 cũng KHÔNG tồn tại (BRD chỉ có FR-ZR-02, dùng cho toàn bộ SS-SCR-012). QnA-09 đã hỏi chung chung về việc rà soát REQ ID Storyboard vs BRD, nhưng chưa nêu đích danh 2 mã cụ thể này — đề nghị BA xác nhận: 2 mã này có mã chính thức tương ứng nào trong BRD, hay cần bổ sung định nghĩa mới cho chúng?</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Đối chiếu toàn văn BRD v0.0.3 — liên quan QnA-09</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát REQ ID cụ thể sau khi có kết quả review testcase)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Toàn bộ TC thuộc SS-SCR-001 (SC1–SC9) dùng REQ ID 'FR-SP-02' và toàn bộ TC thuộc SS-SCR-012 (SC1–SC4) dùng REQ ID có 'FR-ZR-01' — độ tin cậy truy vết REQ ID bị ảnh hưởng cho tới khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Toàn bộ SS-SCR-001-SC1..SC9 (~17 TC), toàn bộ SS-SCR-012-SC1..SC4 (~11 TC)</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>QnA-54</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>KPI-04/06/07 — công thức đo lường cụ thể là gì?</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>BRD chỉ nêu ngưỡng mục tiêu (KPI-04: Tỷ lệ Tìm kiếm sang Giỏ hàng &gt;10%; KPI-06: Tỷ lệ Chỉnh sửa Truy vấn &lt;15-20%; KPI-07: Tỷ lệ Thử lại Tìm kiếm &lt;10-15%), không định nghĩa công thức: 'Tìm kiếm sang Giỏ hàng' tính trên session hay trên từng query? 'Chỉnh sửa Truy vấn' (sửa từ khoá trong cùng phiên) khác 'Thử lại Tìm kiếm' (tìm lại từ đầu) ở event/hành vi cụ thể nào? Cần BA/Data Analytics định nghĩa rõ trước khi có thể đo lường sau go-live.</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>BRD §2.2 Table KPI — chỉ có ngưỡng mục tiêu, không có công thức đo</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>BA / Data Analytics</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Không ảnh hưởng trực tiếp tới Pass/Fail của TC nào trong bộ UI/Integration hiện tại (đây là chỉ số đo sau go-live, không phải hành vi UI có thể test trước khi ra mắt).</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>N/A — thuộc phạm vi Analytics/Instrumentation</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>QnA-55</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005 — giới hạn tối đa số sản phẩm hiển thị trong 1 lần tìm kiếm là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Không tìm thấy quy định nào trong BRD/Storyboard về trần tối đa cho lưới kết quả chính (khác với khối 'Có thể bạn sẽ thích' đã hỏi ở QnA-46, và khối 'Thường mua' hỏi ở QnA-58). Cuộn vô hạn có dừng ở một ngưỡng cụ thể (VD 500/1000 sản phẩm) hay tải tiếp tới hết toàn bộ catalogue khớp?</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005 — không tìm thấy trong BRD/Storyboard</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Chưa có test case nào verify giới hạn tối đa — cần bổ sung TC sau khi có quyết định.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC1, SC1-TC2 (chưa có TC riêng cho giới hạn tối đa)</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>QnA-56</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Trending — từ khoá hot nhưng 0 kết quả catalogue có bị lọc khỏi khối Xu hướng không?</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Phát hiện quan trọng: test case hiện tại SS-SCR-001-SC3-TC3 đang TỰ GIẢ ĐỊNH 'từ khoá 0-kết-quả hoặc vi phạm profanity filter không được hiển thị' — nhưng BRD (FR-PS-02) CHỈ mô tả việc lọc qua Từ điển Cấm (Profanity Filter), KHÔNG hề đề cập tới việc lọc từ khoá cho ra 0 kết quả catalogue. Đây là một giả định do QC tự thêm vào khi viết test case (hợp lý về mặt UX — tránh dẫn khách vào Zero Result ngay từ khối Trending — nhưng chưa được BA xác nhận bằng văn bản). Cần BA xác nhận: quy tắc lọc 0-kết-quả này có thật sự tồn tại, hay từ khoá trending có thể dẫn thẳng khách vào Zero Result Page?</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-PS-02 không đề cập lọc 0-kết-quả — SS-SCR-001-SC3-TC3 đang giả định điều này</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>QC (phát hiện khi rà soát test case đã viết chưa đối chiếu kỹ với BRD)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-001-SC3-TC3 hiện đang test theo giả định của QC, chưa có căn cứ BRD — cần xác nhận lại nội dung Expected Result của TC này (không phải chỉ 1 QnA mới, còn phải rà soát TC cũ).</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-001-SC3-TC3</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>QnA-57</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Trending — một lượt tìm kiếm được tính đếm (count) vào Volume khi nào?</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Khi khách gõ từ khoá rồi nhấn Enter mới được tính 1 lượt tìm kiếm để cộng vào Volume/Velocity score, hay gõ xong bằng bất kỳ cách nào (nhấn Done trên bàn phím, nhấn nút Search, hoặc tap chọn 1 gợi ý Autocomplete) đều được tính? Ảnh hưởng trực tiếp tới độ chính xác của thuật toán chấm điểm Trending (FR-PS-02).</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-PS-02 không định nghĩa event đếm lượt tìm kiếm</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>BA / Data</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Không ảnh hưởng TC nào trong bộ UI hiện tại (đây là logic backend đếm lượt tìm kiếm, không quan sát được qua UI).</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>N/A — thuộc phạm vi backend đếm lượt tìm kiếm</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>QnA-58</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>'Thường mua' (Frequently Purchased) — giới hạn tối đa bao nhiêu SKU khi cuộn tải thêm?</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>FR-PS-03 chỉ mô tả cơ chế: lấy Top 10 SKU còn hàng trước, sau khi khách lướt hết thì tải tiếp lô 10 SKU kế tiếp, 'cứ tiếp tục như thế' — không nêu trần tối đa (tương tự pattern đã hỏi ở QnA-46 cho khối 'Có thể bạn sẽ thích' của Zero Result, và QnA-55 cho trang kết quả chính). Có dừng lại ở một số lượng cụ thể hay tải hết toàn bộ lịch sử mua hàng đủ điều kiện của khách?</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-PS-03 — chỉ mô tả cơ chế lô 10, không nêu giới hạn tối đa</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-001-SC8-TC1 hiện chỉ test việc tải lô kế tiếp, chưa verify giới hạn tối đa cụ thể — cần bổ sung sau khi xác nhận.</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-001-SC8-TC1</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>QnA-59</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Autocomplete — BRD và Storyboard mô tả 2 tiêu chí xếp hạng KHÁC NHAU cho cùng 1 danh sách gợi ý</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Phát hiện quan trọng: BRD (FR-SP-01) mô tả gợi ý autocomplete xếp hạng theo 'keyword xuất hiện ở tên sản phẩm nào nhiều nhất' (tần suất khớp trong catalog), trong khi Storyboard (SS-SCR-002, thành phần #2) lại mô tả 'Sắp xếp theo search volume giảm dần' (độ phổ biến lịch sử tìm kiếm của khách hàng) — đây là 2 TÍN HIỆU HOÀN TOÀN KHÁC NHAU (catalog text-matching vs search-query popularity), không phải chỉ khác cách diễn đạt. Test case hiện tại (SS-SCR-002-SC1-TC3) đã VIẾT THEO HƯỚNG DIỄN GIẢI CỦA STORYBOARD ('từ khoá tìm kiếm phổ biến', không phải 'tên sản phẩm khớp chuỗi') mà chưa đối chiếu với BRD. Ngoài ra không nguồn nào nêu khung thời gian tính 'volume' (all-time hay rolling window, giống các block khác đã hỏi). Cần BA/TD xác nhận tiêu chí chính thức.</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-SP-01 vs Storyboard slide 7 (SS-SCR-002) — 2 mô tả khác nhau cho cùng 1 hành vi</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu BRD với Storyboard khi rà soát test case đã viết)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-002-SC1-TC3 đang thực thi theo diễn giải của Storyboard, chưa được xác nhận là đúng nguồn chính thức — cần rà soát lại một khi có quyết định.</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-002-SC1-TC1, SS-SCR-002-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>QnA-60</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Autocomplete — thứ tự ưu tiên hiển thị giữa khớp từ khoá / đồng nghĩa / đa ngôn ngữ / không dấu / sản phẩm tương tự?</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Khi khách gõ 1 chuỗi, có thể có nhiều LOẠI gợi ý cùng khớp (khớp trực tiếp catalog, từ đồng nghĩa theo FR-SM-04, kết quả đa ngôn ngữ theo FR-SM-02, biến thể không dấu/có dấu theo FR-SM-06, sản phẩm tương tự về ngữ nghĩa) — chưa có tài liệu nào quy định thứ tự ưu tiên hiển thị giữa các loại này trong CÙNG 1 danh sách 10 dòng gợi ý. Câu hỏi con cụ thể: gõ tiếng Việt không dấu, danh sách autocomplete hiển thị lại gợi ý CÓ dấu (chuẩn hoá) hay giữ nguyên không dấu như khách đã gõ? (suy luận hợp lý là có dấu, theo tinh thần FR-SM-06, nhưng chưa được xác nhận rõ cho riêng UI autocomplete).</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-SP-01, FR-SM-02/04/06 — không có quy tắc ưu tiên hiển thị kết hợp</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>BA / UX</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Các test case autocomplete hiện tại (SS-SCR-002-SC1-TC1, TC3, TC4) chỉ test từng loại gợi ý riêng lẻ, chưa test trường hợp NHIỀU loại gợi ý cùng cạnh tranh vị trí hiển thị trong 1 danh sách.</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-002-SC1-TC1, SS-SCR-002-SC1-TC3, SS-SCR-002-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>QnA-61</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>FR-SM-04 Synonym Mapping — ai định nghĩa/duyệt chu kỳ chạy tự động của Data Pipeline?</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>BRD nói: 'Quá trình này được Data Pipeline tự động thực hiện định kỳ. Vận hành viên (OP) không cần phải cấu hình thủ công.' — nhưng không nói rõ: ai quyết định tần suất chạy định kỳ (hàng ngày/hàng tuần?), ai kiểm tra chất lượng các cặp từ đồng nghĩa được tự sinh ra có chính xác không (rủi ro: pipeline tự động có thể tạo ra ánh xạ sai/gây nhiễu kết quả tìm kiếm mà không ai kiểm duyệt).</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-SM-04</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>BA / Data Engineering</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Không có test case UI nào kiểm tra được vấn đề vận hành/quản trị dữ liệu này (không quan sát được qua giao diện khách hàng).</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>N/A — câu hỏi vận hành/quản trị dữ liệu</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>QnA-62</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>FR-PR-01→05 — trọng số Scorecard (Relevance/Purchase Affinity/Margin/Promotion/Trending) được cấu hình/lưu trữ ở đâu?</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Liên quan trực tiếp QnA-52 (Admin Ranking Scorecard ngoài phạm vi Storyboard): nếu màn hình cấu hình trọng số (Admin UI) không nằm trong 19 màn hình của Storyboard, vậy trọng số 40%/20%/15%/15%/10% hiện đang hardcode trong code, hay có 1 kênh cấu hình nào khác (config file, feature flag, DB) chưa được thể hiện trong bộ tài liệu này?</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>BRD §5.2 — liên quan QnA-52</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Không có test case nào kiểm tra được cơ chế cấu hình trọng số (ngoài phạm vi UI khách hàng).</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>N/A — liên quan QnA-52</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>QnA-63</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Sponsored — sản phẩm tài trợ có bắt buộc vẫn liên quan tới từ khoá đang tìm không?</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>QnA-07 đã hỏi về VỊ TRÍ chèn Sponsored (slot cố định hay đấu giá), nhưng chưa hỏi về ĐIỀU KIỆN ĐỦ ĐIỀU KIỆN: sản phẩm Sponsored có bắt buộc phải thuộc tập kết quả liên quan về ngữ nghĩa/catalog tới từ khoá đang tìm, hay nhà cung cấp có thể trả tiền để chèn sản phẩm HOÀN TOÀN KHÔNG LIÊN QUAN vào bất kỳ kết quả tìm kiếm nào?</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-PR-01→05 — mở rộng từ QnA-07</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>PO / Retail Media</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-005-SC2-TC1/TC2 hiện chỉ test nhãn hiển thị và quy tắc out-of-stock cho Sponsored, chưa test điều kiện liên quan ngữ nghĩa.</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC2-TC1, SS-SCR-005-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>QnA-64</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>FR-PR-01→05 — định nghĩa cụ thể của trọng số Margin/Promotion/Trending trong Scorecard là gì?</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>BRD chỉ nêu tỷ trọng % (Margin 15%, Promotion 15%, Trending 10%) nhưng không định nghĩa rõ: Margin tính theo biên lợi nhuận gộp hay ròng, theo SKU hay theo danh mục? Promotion là tín hiệu nhị phân (đang giảm giá/không) hay theo % mức giảm? Trending trong ngữ cảnh Scorecard này có phải cùng thuật toán Trending Score của khối Xu hướng tìm kiếm (FR-PS-02) hay là một tín hiệu độc lập khác (VD lượt xem/mua gần đây của riêng SKU đó)?</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>BRD §5.2 — chỉ có % trọng số, không có định nghĩa</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>BA / Merchandising</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-008-SC1-TC3 (sanity-check AI ranking) chỉ verify hành vi bề mặt (thứ tự khác sort đơn giản), không thể verify đúng-sai từng thành phần trọng số cho tới khi có định nghĩa.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>QnA-65</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>AI Scorecard (FR-PR-01) chỉ áp dụng cho tuỳ chọn Sort 'Liên quan nhất', hay ảnh hưởng cả 7 tuỳ chọn Sort khác?</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>FR-PR-01 mô tả thuật toán Scorecard chấm điểm sản phẩm nhưng không nói rõ PHẠM VI áp dụng. FR-PR-06 (Sorting Options) nói rõ 7 tuỳ chọn còn lại (Bán chạy nhất, Giá, Đánh giá, Tên...) 'giữ nguyên logic sorting như hệ thống cũ' — ngụ ý Scorecard CHỈ áp dụng cho 'Liên quan nhất', nhưng cần BA xác nhận minh bạch: liệu Out-of-stock override và Sponsored override (là 1 phần của Scorecard theo FR-PR-01→05) có áp dụng ĐỒNG THỜI cho cả 7 sort thủ công kia không (VD sản phẩm hết hàng có luôn bị đẩy xuống đáy dù đang sort theo Giá thấp-cao)?</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>BRD FR-PR-01 vs FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Các test case SS-SCR-008-SC1-TC3 đến TC10 (verify từng sort option) mới chỉ test đúng thứ tự CHÍNH của mỗi tiêu chí, chưa test rõ Out-of-stock/Sponsored override có áp dụng xuyên suốt cả 7 sort thủ công hay không.</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3, TC4, TC5, TC6, TC7, TC8, TC9, TC10 — liên quan QnA-37</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>QnA-66</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>REQ chi tiết của FR-SF-01, FR-SF-02, FR-SF-03 (Smart Filter) — đang bị gộp chung, cần tách rõ từng mã</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Giống pattern đã xử lý ở QnA-32 (FR-GD-01/03): BRD gộp FR-SF-01, FR-SF-02, FR-SF-03 vào chung 1 dòng mô tả duy nhất ('[Bộ lọc Thông minh] AI bốc ra tối đa 10 Tag lọc thông minh có Information Gain cao nhất... cấu trúc phẳng, không gom nhóm... Filter hiển thị bắt buộc phải trả về &gt;=1 sản phẩm.'), không tách bạch nội dung nào ứng với mã nào trong 3 mã. Đề nghị BA tách rõ để trace test case chính xác hơn — hiện toàn bộ TC liên quan Smart Filter đang dùng chung chuỗi 'FR-SF-01, FR-SF-04' không phân biệt được.</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>BRD §5.2 'FR-SF-01 -&gt; FR-SF-03'</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát bổ sung)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Cột REQ ID của toàn bộ TC liên quan Smart Filter (SS-SCR-005-SC9, SS-SCR-009-SC1/SC3) không tách bạch được theo từng mã con.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC1-TC1, SS-SCR-009-SC3-TC1, SS-SCR-009-SC3-TC2, SS-SCR-005-SC9-TC1, SS-SCR-005-SC9-TC2</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>QnA-67</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ NFR-002 (150ms) mâu thuẫn với KPI-02 (&lt;300ms) cho cùng 1 chỉ số 'thời gian phản hồi autocomplete' — và test case hiện tại đang trích dẫn sai số</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>BRD ghi 2 số khác nhau cho cùng 1 phép đo: NFR-002 = '95% autocomplete trả gợi ý trong vòng 150ms'; KPI-02 = 'Gợi ý Trong khi Nhập, Dưới 0,3 giây (không bao gồm khoảng thời gian debounce 0,3 giây)' = &lt;300ms. Cả 2 đều mô tả thời gian phản hồi SAU KHI debounce đã trôi qua — chênh lệch 2x, không phải làm tròn. NGHIÊM TRỌNG HƠN: test case hiện tại của bộ này (SS-SCR-002-SC1-TC1) đang trích dẫn '≤300ms... (P95, NFR-002)' — TỨC ĐANG GÁN SAI số 300ms cho NFR-002 (số đúng theo văn bản BRD là 150ms, số 300ms thực ra khớp với KPI-02). Cần BA chốt ngay số chính thức, sau đó QC sẽ rà soát lại TC hiện có cho khớp.</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>BRD NFR-002 vs KPI-02 — ảnh hưởng SS-SCR-002-SC1-TC1 hiện có (đang trích dẫn sai REQ ID/số liệu)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>QC (đối chiếu số liệu khi rà soát testcase)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>BA / TD</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Test case SS-SCR-002-SC1-TC1 đang test &amp; trích dẫn ngưỡng SAI theo văn bản BRD (300ms gán cho NFR-002 trong khi BRD ghi 150ms) — cần sửa lại TC này sau khi BA xác nhận số chính thức, dù hiện tại KHÔNG chặn Pass/Fail (300ms vẫn có căn cứ từ KPI-02, chỉ là gán nhầm REQ ID).</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-002-SC1-TC1</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Tổng số QnA:</t>
         </is>
       </c>
-      <c r="B34" s="5">
-        <f>COUNTA(A5:A32)</f>
+      <c r="B73" s="5">
+        <f>COUNTA(A5:A71)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Đang mở (Open):</t>
         </is>
       </c>
-      <c r="B35" s="5">
-        <f>COUNTIF(G5:G32,"Open")</f>
+      <c r="B74" s="5">
+        <f>COUNTIF(G5:G71,"Open")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Đã trả lời (Resolved):</t>
         </is>
       </c>
-      <c r="B36" s="5">
-        <f>COUNTIF(G5:G32,"Resolved")</f>
+      <c r="B75" s="5">
+        <f>COUNTIF(G5:G71,"Resolved")</f>
         <v/>
       </c>
     </row>
